--- a/GBDS JUNE FILES 2026/GBDS UPDATED DOS - JUNE 2026.xlsx
+++ b/GBDS JUNE FILES 2026/GBDS UPDATED DOS - JUNE 2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\GBDS JUNE FILES 2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6F10281A-CA64-46C7-A47C-F0446C86B5A1}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{39D0F18C-4E71-4FC7-8EFF-1FF16B994FAE}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{EAA847CC-C244-4239-B005-CBB8C204AC80}"/>
   </bookViews>
@@ -9204,16 +9204,18 @@
       <c r="L13" s="50">
         <v>4.5</v>
       </c>
-      <c r="M13" s="51"/>
+      <c r="M13" s="51">
+        <v>108</v>
+      </c>
       <c r="N13" s="51"/>
       <c r="O13" s="51"/>
       <c r="P13" s="52" t="str">
         <f t="shared" ref="P13:P68" si="5">IF(M13&amp;N13="","",ROUND(((M13+N13)/G13),1)&amp;" pallets")</f>
-        <v/>
+        <v>1 pallets</v>
       </c>
       <c r="Q13" s="53">
         <f t="shared" ref="Q13:Q70" si="6">(J13*M13)+(K13*N13)+(O13*L13)</f>
-        <v>0</v>
+        <v>11988</v>
       </c>
       <c r="S13" s="54"/>
       <c r="T13" s="54"/>
@@ -9271,17 +9273,19 @@
         <f t="shared" si="2"/>
         <v>1093</v>
       </c>
-      <c r="F14" s="46"/>
+      <c r="F14" s="46">
+        <v>252</v>
+      </c>
       <c r="G14" s="47">
         <v>63</v>
       </c>
       <c r="H14" s="64" t="str">
         <f>IF(F14="","",(ROUND((F14/G14),1)&amp;" pallets"))</f>
-        <v/>
+        <v>4 pallets</v>
       </c>
       <c r="I14" s="49">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>275436</v>
       </c>
       <c r="J14" s="50">
         <v>120</v>
@@ -9292,31 +9296,33 @@
       <c r="L14" s="50">
         <v>1.5</v>
       </c>
-      <c r="M14" s="51"/>
+      <c r="M14" s="51">
+        <v>63</v>
+      </c>
       <c r="N14" s="51"/>
       <c r="O14" s="51"/>
       <c r="P14" s="52" t="str">
         <f t="shared" si="5"/>
-        <v/>
+        <v>1 pallets</v>
       </c>
       <c r="Q14" s="53">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>7560</v>
       </c>
       <c r="S14" s="54"/>
       <c r="T14" s="54"/>
       <c r="U14" s="55"/>
       <c r="X14" s="56">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>245196</v>
       </c>
       <c r="Y14" s="57">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>8081.64</v>
       </c>
       <c r="Z14" s="36">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>882</v>
       </c>
       <c r="AA14" s="37"/>
       <c r="AB14" s="58">
@@ -9359,14 +9365,16 @@
         <f t="shared" si="2"/>
         <v>781</v>
       </c>
-      <c r="F15" s="46"/>
+      <c r="F15" s="46">
+        <v>384</v>
+      </c>
       <c r="G15" s="47">
         <v>96</v>
       </c>
       <c r="H15" s="64"/>
       <c r="I15" s="49">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>299904</v>
       </c>
       <c r="J15" s="50">
         <v>111</v>
@@ -9393,15 +9401,15 @@
       <c r="U15" s="55"/>
       <c r="X15" s="56">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>257280</v>
       </c>
       <c r="Y15" s="57">
         <f>F15*AI15</f>
-        <v>0</v>
+        <v>11558.400000000001</v>
       </c>
       <c r="Z15" s="36">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>1344</v>
       </c>
       <c r="AA15" s="37"/>
       <c r="AB15" s="58">
@@ -9444,14 +9452,16 @@
         <f t="shared" si="2"/>
         <v>761</v>
       </c>
-      <c r="F16" s="46"/>
+      <c r="F16" s="46">
+        <v>972</v>
+      </c>
       <c r="G16" s="47">
         <v>108</v>
       </c>
       <c r="H16" s="64"/>
       <c r="I16" s="49">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>739692</v>
       </c>
       <c r="J16" s="50">
         <v>111</v>
@@ -9460,31 +9470,33 @@
       <c r="L16" s="50">
         <v>4.5</v>
       </c>
-      <c r="M16" s="51"/>
+      <c r="M16" s="51">
+        <v>1296</v>
+      </c>
       <c r="N16" s="193"/>
       <c r="O16" s="51"/>
       <c r="P16" s="52" t="str">
         <f t="shared" si="5"/>
-        <v/>
+        <v>12 pallets</v>
       </c>
       <c r="Q16" s="53">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>143856</v>
       </c>
       <c r="S16" s="54"/>
       <c r="T16" s="67"/>
       <c r="U16" s="55"/>
       <c r="X16" s="56">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>631800</v>
       </c>
       <c r="Y16" s="57">
         <f>F16*AI16</f>
-        <v>0</v>
+        <v>28810.080000000002</v>
       </c>
       <c r="Z16" s="36">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>3402</v>
       </c>
       <c r="AA16" s="37"/>
       <c r="AB16" s="58">
@@ -13840,7 +13852,7 @@
       <c r="G71" s="239"/>
       <c r="H71" s="147" t="str">
         <f>ROUND(((F12+F30+F52+F57+F58+F59+F60+F61)/72+(F13+F16+F18)/108+(F14+SUM(F19:F29)+F31+F32+F22+F50+F45)/63+F15/96+SUM(F34:F43)/100+SUM(F47:F49)/24+SUM(F62:F68)/100+(F51+F46+F44)/100),1)&amp;" pallets"</f>
-        <v>0 pallets</v>
+        <v>17 pallets</v>
       </c>
       <c r="I71" s="148"/>
       <c r="J71" s="149"/>
@@ -13851,7 +13863,7 @@
       <c r="O71" s="152"/>
       <c r="P71" s="196" t="str">
         <f>ROUND((((M12+N12+M30+M57+M58+M59+M60+M61+N57)/72+(M13+N13+M16+M18)/108+(M15+N15)/96+SUM(M14,M19:M29,M31:M32,M50,N14)/63)),1)&amp;" pallets"</f>
-        <v>0 pallets</v>
+        <v>14 pallets</v>
       </c>
       <c r="Q71" s="153"/>
       <c r="R71" s="152"/>
@@ -13915,7 +13927,7 @@
       <c r="E73" s="157"/>
       <c r="F73" s="230">
         <f>SUM(I12:I70)</f>
-        <v>0</v>
+        <v>1315032</v>
       </c>
       <c r="G73" s="230"/>
       <c r="H73" s="230"/>
@@ -13929,7 +13941,7 @@
       <c r="N73" s="233"/>
       <c r="O73" s="230">
         <f>SUM(Q12:Q70)</f>
-        <v>0</v>
+        <v>163404</v>
       </c>
       <c r="P73" s="230"/>
       <c r="Q73" s="231"/>
@@ -13939,7 +13951,7 @@
       </c>
       <c r="T73" s="234">
         <f>SUM(Y12:Y68)</f>
-        <v>0</v>
+        <v>48450.12</v>
       </c>
       <c r="U73" s="235"/>
       <c r="V73" s="160"/>
@@ -13999,7 +14011,7 @@
       <c r="E75" s="157"/>
       <c r="F75" s="230">
         <f>SUM(I14:I72)</f>
-        <v>0</v>
+        <v>1315032</v>
       </c>
       <c r="G75" s="230"/>
       <c r="H75" s="230"/>
@@ -14013,7 +14025,7 @@
       <c r="N75" s="233"/>
       <c r="O75" s="230">
         <f>SUM(Q14:Q72)</f>
-        <v>0</v>
+        <v>151416</v>
       </c>
       <c r="P75" s="230"/>
       <c r="Q75" s="231"/>
@@ -14023,7 +14035,7 @@
       </c>
       <c r="T75" s="234">
         <f>SUM(Z12:Z70)</f>
-        <v>0</v>
+        <v>5628</v>
       </c>
       <c r="U75" s="235"/>
       <c r="V75" s="160"/>
@@ -14083,7 +14095,7 @@
       <c r="E77" s="157"/>
       <c r="F77" s="230">
         <f>IF(U7&gt;0,"",(F73-O73-T79-P79))</f>
-        <v>0</v>
+        <v>1097549.8799999999</v>
       </c>
       <c r="G77" s="230"/>
       <c r="H77" s="230"/>
@@ -14189,7 +14201,7 @@
       </c>
       <c r="T79" s="234">
         <f>T77+T73+T75</f>
-        <v>0</v>
+        <v>54078.12</v>
       </c>
       <c r="U79" s="235"/>
       <c r="V79" s="160"/>
@@ -14528,6 +14540,7 @@
     <row r="100" ht="12.75" x14ac:dyDescent="0.25"/>
   </sheetData>
   <mergeCells count="66">
+    <mergeCell ref="M10:Q10"/>
     <mergeCell ref="F2:S2"/>
     <mergeCell ref="W2:W4"/>
     <mergeCell ref="F4:M4"/>
@@ -14535,12 +14548,6 @@
     <mergeCell ref="F6:M6"/>
     <mergeCell ref="W6:W7"/>
     <mergeCell ref="F7:M7"/>
-    <mergeCell ref="B9:B11"/>
-    <mergeCell ref="C9:C11"/>
-    <mergeCell ref="D9:D11"/>
-    <mergeCell ref="E9:E11"/>
-    <mergeCell ref="F9:Q9"/>
-    <mergeCell ref="M10:Q10"/>
     <mergeCell ref="AG9:AG11"/>
     <mergeCell ref="AI9:AI11"/>
     <mergeCell ref="F10:F11"/>
@@ -14568,6 +14575,11 @@
     <mergeCell ref="M73:N73"/>
     <mergeCell ref="O73:Q73"/>
     <mergeCell ref="T73:U73"/>
+    <mergeCell ref="B9:B11"/>
+    <mergeCell ref="C9:C11"/>
+    <mergeCell ref="D9:D11"/>
+    <mergeCell ref="E9:E11"/>
+    <mergeCell ref="F9:Q9"/>
     <mergeCell ref="W77:W79"/>
     <mergeCell ref="F79:I79"/>
     <mergeCell ref="M79:N79"/>

--- a/GBDS JUNE FILES 2026/GBDS UPDATED DOS - JUNE 2026.xlsx
+++ b/GBDS JUNE FILES 2026/GBDS UPDATED DOS - JUNE 2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\GBDS JUNE FILES 2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{39D0F18C-4E71-4FC7-8EFF-1FF16B994FAE}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E55F8AFA-B83E-4239-A78F-C6E0012B72F8}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{EAA847CC-C244-4239-B005-CBB8C204AC80}"/>
   </bookViews>
@@ -8677,7 +8677,7 @@
     <col min="14" max="14" width="19.5703125" style="2" customWidth="1"/>
     <col min="15" max="15" width="24.140625" style="2" customWidth="1"/>
     <col min="16" max="16" width="18.7109375" style="2" customWidth="1"/>
-    <col min="17" max="17" width="18.7109375" style="3" customWidth="1"/>
+    <col min="17" max="17" width="19.28515625" style="3" bestFit="1" customWidth="1"/>
     <col min="18" max="18" width="2.140625" style="2" customWidth="1"/>
     <col min="19" max="21" width="18.7109375" style="2" customWidth="1"/>
     <col min="22" max="22" width="2.7109375" style="2" customWidth="1"/>
